--- a/DeudoresPrueba.xlsx
+++ b/DeudoresPrueba.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>Consecutivo</t>
   </si>
@@ -31,18 +31,9 @@
     <t>Pagado</t>
   </si>
   <si>
-    <t>ABEL POLLO</t>
-  </si>
-  <si>
     <t>ALISO</t>
   </si>
   <si>
-    <t>CAMILIN</t>
-  </si>
-  <si>
-    <t>CAMPO VERDE TOCANCIPA</t>
-  </si>
-  <si>
     <t>CARNES JOHANA</t>
   </si>
   <si>
@@ -67,6 +58,9 @@
     <t>DOÑA SANDRA</t>
   </si>
   <si>
+    <t>EL RES</t>
+  </si>
+  <si>
     <t>EL RUBY</t>
   </si>
   <si>
@@ -100,10 +94,10 @@
     <t>PLAZA JESSICA</t>
   </si>
   <si>
-    <t>PREMIUM</t>
-  </si>
-  <si>
     <t>PUNTA DE ANCA</t>
+  </si>
+  <si>
+    <t>SANTANDER SUR</t>
   </si>
 </sst>
 </file>
@@ -465,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -493,10 +487,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2">
-        <v>46046</v>
+        <v>46049</v>
       </c>
       <c r="D2">
-        <v>83000</v>
+        <v>131000</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -510,10 +504,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="2">
-        <v>46048</v>
+        <v>46045</v>
       </c>
       <c r="D3">
-        <v>100000</v>
+        <v>164000</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -527,10 +521,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="2">
-        <v>46046</v>
+        <v>46049</v>
       </c>
       <c r="D4">
-        <v>545000</v>
+        <v>164000</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -544,10 +538,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="2">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="D5">
-        <v>285000</v>
+        <v>403800</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -561,10 +555,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="D6">
-        <v>164000</v>
+        <v>170000</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -575,13 +569,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="D7">
-        <v>280000</v>
+        <v>170000</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -592,13 +586,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="D8">
-        <v>426500</v>
+        <v>1000000</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -612,10 +606,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="2">
-        <v>46045</v>
+        <v>45921</v>
       </c>
       <c r="D9">
-        <v>403800</v>
+        <v>200000</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -629,10 +623,10 @@
         <v>12</v>
       </c>
       <c r="C10" s="2">
-        <v>46047</v>
+        <v>45947</v>
       </c>
       <c r="D10">
-        <v>170000</v>
+        <v>100000</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -646,10 +640,10 @@
         <v>13</v>
       </c>
       <c r="C11" s="2">
-        <v>46042</v>
+        <v>46039</v>
       </c>
       <c r="D11">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -663,10 +657,10 @@
         <v>14</v>
       </c>
       <c r="C12" s="2">
-        <v>45921</v>
+        <v>46049</v>
       </c>
       <c r="D12">
-        <v>200000</v>
+        <v>264000</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -680,10 +674,10 @@
         <v>15</v>
       </c>
       <c r="C13" s="2">
-        <v>45947</v>
+        <v>46048</v>
       </c>
       <c r="D13">
-        <v>100000</v>
+        <v>107000</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -697,10 +691,10 @@
         <v>16</v>
       </c>
       <c r="C14" s="2">
-        <v>46039</v>
+        <v>45996</v>
       </c>
       <c r="D14">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -714,10 +708,10 @@
         <v>17</v>
       </c>
       <c r="C15" s="2">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="D15">
-        <v>188000</v>
+        <v>560000</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -731,10 +725,10 @@
         <v>18</v>
       </c>
       <c r="C16" s="2">
-        <v>45996</v>
+        <v>46042</v>
       </c>
       <c r="D16">
-        <v>20000</v>
+        <v>264000</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -748,10 +742,10 @@
         <v>19</v>
       </c>
       <c r="C17" s="2">
-        <v>46046</v>
+        <v>45912</v>
       </c>
       <c r="D17">
-        <v>560000</v>
+        <v>82000</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -765,10 +759,10 @@
         <v>20</v>
       </c>
       <c r="C18" s="2">
-        <v>46042</v>
+        <v>45988</v>
       </c>
       <c r="D18">
-        <v>264000</v>
+        <v>15400</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -779,13 +773,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="2">
-        <v>45912</v>
+        <v>45995</v>
       </c>
       <c r="D19">
-        <v>82000</v>
+        <v>339000</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -796,13 +790,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2">
-        <v>45995</v>
+        <v>46031</v>
       </c>
       <c r="D20">
-        <v>339000</v>
+        <v>21900</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -813,13 +807,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="2">
-        <v>45988</v>
+        <v>46038</v>
       </c>
       <c r="D21">
-        <v>15400</v>
+        <v>175800</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -830,13 +824,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="2">
-        <v>46031</v>
+        <v>46048</v>
       </c>
       <c r="D22">
-        <v>21900</v>
+        <v>235000</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -850,10 +844,10 @@
         <v>23</v>
       </c>
       <c r="C23" s="2">
-        <v>46038</v>
+        <v>45931</v>
       </c>
       <c r="D23">
-        <v>175800</v>
+        <v>82000</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -867,10 +861,10 @@
         <v>24</v>
       </c>
       <c r="C24" s="2">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="D24">
-        <v>173000</v>
+        <v>148000</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -884,10 +878,10 @@
         <v>25</v>
       </c>
       <c r="C25" s="2">
-        <v>45931</v>
+        <v>46047</v>
       </c>
       <c r="D25">
-        <v>82000</v>
+        <v>1344000</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -901,10 +895,10 @@
         <v>26</v>
       </c>
       <c r="C26" s="2">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="D26">
-        <v>148000</v>
+        <v>965000</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -918,46 +912,12 @@
         <v>27</v>
       </c>
       <c r="C27" s="2">
-        <v>46047</v>
+        <v>46049</v>
       </c>
       <c r="D27">
-        <v>1344000</v>
+        <v>100000</v>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="2">
-        <v>46046</v>
-      </c>
-      <c r="D28">
-        <v>178000</v>
-      </c>
-      <c r="E28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="2">
-        <v>46045</v>
-      </c>
-      <c r="D29">
-        <v>965000</v>
-      </c>
-      <c r="E29" t="b">
         <v>0</v>
       </c>
     </row>

--- a/DeudoresPrueba.xlsx
+++ b/DeudoresPrueba.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>Consecutivo</t>
   </si>
@@ -31,9 +31,21 @@
     <t>Pagado</t>
   </si>
   <si>
+    <t>ALAMO</t>
+  </si>
+  <si>
     <t>ALISO</t>
   </si>
   <si>
+    <t>BULL RUNG</t>
+  </si>
+  <si>
+    <t>CAMPO VERDE TOCANCIPA</t>
+  </si>
+  <si>
+    <t>CAMPO VERDE ZIPAQUIRA</t>
+  </si>
+  <si>
     <t>CARNES JOHANA</t>
   </si>
   <si>
@@ -64,21 +76,33 @@
     <t>EL RUBY</t>
   </si>
   <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
     <t>JUAN DAVID</t>
   </si>
   <si>
-    <t>JULIANA POLLO</t>
+    <t>LA PAISA</t>
+  </si>
+  <si>
+    <t>LA PAMPA</t>
   </si>
   <si>
     <t>LA SELECTA</t>
   </si>
   <si>
+    <t>LOS PAISANOS</t>
+  </si>
+  <si>
+    <t>MAFE</t>
+  </si>
+  <si>
+    <t>MERKA FRUVER ALEJANDRO</t>
+  </si>
+  <si>
     <t>MERKA FRUVER DEXI</t>
   </si>
   <si>
+    <t>MULTICARNES</t>
+  </si>
+  <si>
     <t>NEVADA</t>
   </si>
   <si>
@@ -98,6 +122,9 @@
   </si>
   <si>
     <t>SANTANDER SUR</t>
+  </si>
+  <si>
+    <t>WILLINTON</t>
   </si>
 </sst>
 </file>
@@ -459,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -487,10 +514,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="D2">
-        <v>131000</v>
+        <v>174000</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -504,10 +531,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="2">
-        <v>46045</v>
+        <v>46053</v>
       </c>
       <c r="D3">
-        <v>164000</v>
+        <v>113000</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -521,10 +548,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="2">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="D4">
-        <v>164000</v>
+        <v>88900</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -538,10 +565,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="2">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="D5">
-        <v>403800</v>
+        <v>540000</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -555,10 +582,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="D6">
-        <v>170000</v>
+        <v>874300</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -569,13 +596,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2">
-        <v>46047</v>
+        <v>46052</v>
       </c>
       <c r="D7">
-        <v>170000</v>
+        <v>91200</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -589,10 +616,10 @@
         <v>10</v>
       </c>
       <c r="C8" s="2">
-        <v>46042</v>
+        <v>46045</v>
       </c>
       <c r="D8">
-        <v>1000000</v>
+        <v>164000</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -606,10 +633,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="2">
-        <v>45921</v>
+        <v>46053</v>
       </c>
       <c r="D9">
-        <v>200000</v>
+        <v>390600</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -623,10 +650,10 @@
         <v>12</v>
       </c>
       <c r="C10" s="2">
-        <v>45947</v>
+        <v>46052</v>
       </c>
       <c r="D10">
-        <v>100000</v>
+        <v>446600</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -640,10 +667,10 @@
         <v>13</v>
       </c>
       <c r="C11" s="2">
-        <v>46039</v>
+        <v>46053</v>
       </c>
       <c r="D11">
-        <v>100000</v>
+        <v>255000</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -657,10 +684,10 @@
         <v>14</v>
       </c>
       <c r="C12" s="2">
-        <v>46049</v>
+        <v>46042</v>
       </c>
       <c r="D12">
-        <v>264000</v>
+        <v>1000000</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -674,10 +701,10 @@
         <v>15</v>
       </c>
       <c r="C13" s="2">
-        <v>46048</v>
+        <v>45921</v>
       </c>
       <c r="D13">
-        <v>107000</v>
+        <v>200000</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -691,10 +718,10 @@
         <v>16</v>
       </c>
       <c r="C14" s="2">
-        <v>45996</v>
+        <v>45947</v>
       </c>
       <c r="D14">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -708,10 +735,10 @@
         <v>17</v>
       </c>
       <c r="C15" s="2">
-        <v>46046</v>
+        <v>46039</v>
       </c>
       <c r="D15">
-        <v>560000</v>
+        <v>100000</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -725,7 +752,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="2">
-        <v>46042</v>
+        <v>46049</v>
       </c>
       <c r="D16">
         <v>264000</v>
@@ -742,10 +769,10 @@
         <v>19</v>
       </c>
       <c r="C17" s="2">
-        <v>45912</v>
+        <v>46048</v>
       </c>
       <c r="D17">
-        <v>82000</v>
+        <v>107000</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -759,10 +786,10 @@
         <v>20</v>
       </c>
       <c r="C18" s="2">
-        <v>45988</v>
+        <v>46046</v>
       </c>
       <c r="D18">
-        <v>15400</v>
+        <v>560000</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -773,13 +800,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" s="2">
-        <v>45995</v>
+        <v>46051</v>
       </c>
       <c r="D19">
-        <v>339000</v>
+        <v>725000</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -790,13 +817,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" s="2">
-        <v>46031</v>
+        <v>46052</v>
       </c>
       <c r="D20">
-        <v>21900</v>
+        <v>230700</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -807,13 +834,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C21" s="2">
-        <v>46038</v>
+        <v>45912</v>
       </c>
       <c r="D21">
-        <v>175800</v>
+        <v>82000</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -824,13 +851,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C22" s="2">
-        <v>46048</v>
+        <v>46051</v>
       </c>
       <c r="D22">
-        <v>235000</v>
+        <v>328000</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -841,13 +868,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C23" s="2">
-        <v>45931</v>
+        <v>46051</v>
       </c>
       <c r="D23">
-        <v>82000</v>
+        <v>50000</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -858,13 +885,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C24" s="2">
-        <v>46046</v>
+        <v>46051</v>
       </c>
       <c r="D24">
-        <v>148000</v>
+        <v>510100</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -875,13 +902,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C25" s="2">
-        <v>46047</v>
+        <v>45995</v>
       </c>
       <c r="D25">
-        <v>1344000</v>
+        <v>339000</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -892,13 +919,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2">
-        <v>46045</v>
+        <v>45988</v>
       </c>
       <c r="D26">
-        <v>965000</v>
+        <v>15400</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -909,15 +936,168 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="2">
+        <v>46052</v>
+      </c>
+      <c r="D27">
+        <v>443900</v>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="C27" s="2">
-        <v>46049</v>
-      </c>
-      <c r="D27">
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2">
+        <v>46052</v>
+      </c>
+      <c r="D28">
+        <v>410800</v>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="2">
+        <v>46052</v>
+      </c>
+      <c r="D29">
+        <v>200000</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="2">
+        <v>45931</v>
+      </c>
+      <c r="D30">
+        <v>82000</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="2">
+        <v>46053</v>
+      </c>
+      <c r="D31">
         <v>100000</v>
       </c>
-      <c r="E27" t="b">
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="2">
+        <v>46047</v>
+      </c>
+      <c r="D32">
+        <v>200000</v>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="2">
+        <v>46052</v>
+      </c>
+      <c r="D33">
+        <v>1881400</v>
+      </c>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="2">
+        <v>46052</v>
+      </c>
+      <c r="D34">
+        <v>700000</v>
+      </c>
+      <c r="E34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="2">
+        <v>46053</v>
+      </c>
+      <c r="D35">
+        <v>329000</v>
+      </c>
+      <c r="E35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="2">
+        <v>46053</v>
+      </c>
+      <c r="D36">
+        <v>67000</v>
+      </c>
+      <c r="E36" t="b">
         <v>0</v>
       </c>
     </row>

--- a/DeudoresPrueba.xlsx
+++ b/DeudoresPrueba.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Consecutivo</t>
   </si>
@@ -37,9 +37,6 @@
     <t>ALISO</t>
   </si>
   <si>
-    <t>BULL RUNG</t>
-  </si>
-  <si>
     <t>CAMPO VERDE TOCANCIPA</t>
   </si>
   <si>
@@ -55,12 +52,12 @@
     <t>CIMARRON DORADO</t>
   </si>
   <si>
+    <t>CLIENTE PAOLA</t>
+  </si>
+  <si>
     <t>COCINA CHINA</t>
   </si>
   <si>
-    <t>CRISTIAN ACACIAS</t>
-  </si>
-  <si>
     <t>DARWIN FUTBOL</t>
   </si>
   <si>
@@ -70,33 +67,27 @@
     <t>DOÑA SANDRA</t>
   </si>
   <si>
-    <t>EL RES</t>
+    <t>EL CEBU</t>
   </si>
   <si>
     <t>EL RUBY</t>
   </si>
   <si>
+    <t>FERROCAM</t>
+  </si>
+  <si>
     <t>JUAN DAVID</t>
   </si>
   <si>
-    <t>LA PAISA</t>
-  </si>
-  <si>
     <t>LA PAMPA</t>
   </si>
   <si>
     <t>LA SELECTA</t>
   </si>
   <si>
-    <t>LOS PAISANOS</t>
-  </si>
-  <si>
     <t>MAFE</t>
   </si>
   <si>
-    <t>MERKA FRUVER ALEJANDRO</t>
-  </si>
-  <si>
     <t>MERKA FRUVER DEXI</t>
   </si>
   <si>
@@ -122,9 +113,6 @@
   </si>
   <si>
     <t>SANTANDER SUR</t>
-  </si>
-  <si>
-    <t>WILLINTON</t>
   </si>
 </sst>
 </file>
@@ -486,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -531,10 +519,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="2">
-        <v>46053</v>
+        <v>46055</v>
       </c>
       <c r="D3">
-        <v>113000</v>
+        <v>63000</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -551,7 +539,7 @@
         <v>46051</v>
       </c>
       <c r="D4">
-        <v>88900</v>
+        <v>540000</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -568,7 +556,7 @@
         <v>46051</v>
       </c>
       <c r="D5">
-        <v>540000</v>
+        <v>874300</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -582,10 +570,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="D6">
-        <v>874300</v>
+        <v>324500</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -599,10 +587,10 @@
         <v>10</v>
       </c>
       <c r="C7" s="2">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="D7">
-        <v>91200</v>
+        <v>620000</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -613,13 +601,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2">
-        <v>46045</v>
+        <v>46056</v>
       </c>
       <c r="D8">
-        <v>164000</v>
+        <v>307000</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -630,13 +618,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2">
-        <v>46053</v>
+        <v>46056</v>
       </c>
       <c r="D9">
-        <v>390600</v>
+        <v>122500</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -647,13 +635,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="2">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="D10">
-        <v>446600</v>
+        <v>255000</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -664,13 +652,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2">
-        <v>46053</v>
+        <v>45921</v>
       </c>
       <c r="D11">
-        <v>255000</v>
+        <v>200000</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -681,13 +669,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="2">
-        <v>46042</v>
+        <v>45947</v>
       </c>
       <c r="D12">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -698,13 +686,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="2">
-        <v>45921</v>
+        <v>46039</v>
       </c>
       <c r="D13">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -715,13 +703,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="2">
-        <v>45947</v>
+        <v>46056</v>
       </c>
       <c r="D14">
-        <v>100000</v>
+        <v>298000</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -732,13 +720,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="2">
-        <v>46039</v>
+        <v>46048</v>
       </c>
       <c r="D15">
-        <v>100000</v>
+        <v>107000</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -749,13 +737,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="2">
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="D16">
-        <v>264000</v>
+        <v>257700</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -766,13 +754,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="2">
-        <v>46048</v>
+        <v>46056</v>
       </c>
       <c r="D17">
-        <v>107000</v>
+        <v>4101500</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -783,13 +771,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2">
-        <v>46046</v>
+        <v>46052</v>
       </c>
       <c r="D18">
-        <v>560000</v>
+        <v>230700</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -800,13 +788,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="2">
-        <v>46051</v>
+        <v>45912</v>
       </c>
       <c r="D19">
-        <v>725000</v>
+        <v>82000</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -817,13 +805,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" s="2">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="D20">
-        <v>230700</v>
+        <v>50000</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -834,13 +822,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" s="2">
-        <v>45912</v>
+        <v>45988</v>
       </c>
       <c r="D21">
-        <v>82000</v>
+        <v>15400</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -854,10 +842,10 @@
         <v>24</v>
       </c>
       <c r="C22" s="2">
-        <v>46051</v>
+        <v>45995</v>
       </c>
       <c r="D22">
-        <v>328000</v>
+        <v>339000</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -871,10 +859,10 @@
         <v>25</v>
       </c>
       <c r="C23" s="2">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="D23">
-        <v>50000</v>
+        <v>443900</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -888,10 +876,10 @@
         <v>26</v>
       </c>
       <c r="C24" s="2">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="D24">
-        <v>510100</v>
+        <v>193800</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -905,10 +893,10 @@
         <v>27</v>
       </c>
       <c r="C25" s="2">
-        <v>45995</v>
+        <v>46055</v>
       </c>
       <c r="D25">
-        <v>339000</v>
+        <v>116000</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -919,13 +907,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" s="2">
-        <v>45988</v>
+        <v>45931</v>
       </c>
       <c r="D26">
-        <v>15400</v>
+        <v>82000</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -936,13 +924,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C27" s="2">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="D27">
-        <v>443900</v>
+        <v>100000</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -953,13 +941,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C28" s="2">
         <v>46052</v>
       </c>
       <c r="D28">
-        <v>410800</v>
+        <v>1881400</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -970,13 +958,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C29" s="2">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="D29">
-        <v>200000</v>
+        <v>700400</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -987,117 +975,15 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C30" s="2">
-        <v>45931</v>
+        <v>46056</v>
       </c>
       <c r="D30">
-        <v>82000</v>
+        <v>176000</v>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="2">
-        <v>46053</v>
-      </c>
-      <c r="D31">
-        <v>100000</v>
-      </c>
-      <c r="E31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="2">
-        <v>46047</v>
-      </c>
-      <c r="D32">
-        <v>200000</v>
-      </c>
-      <c r="E32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="2">
-        <v>46052</v>
-      </c>
-      <c r="D33">
-        <v>1881400</v>
-      </c>
-      <c r="E33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="2">
-        <v>46052</v>
-      </c>
-      <c r="D34">
-        <v>700000</v>
-      </c>
-      <c r="E34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="2">
-        <v>46053</v>
-      </c>
-      <c r="D35">
-        <v>329000</v>
-      </c>
-      <c r="E35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="2">
-        <v>46053</v>
-      </c>
-      <c r="D36">
-        <v>67000</v>
-      </c>
-      <c r="E36" t="b">
         <v>0</v>
       </c>
     </row>

--- a/DeudoresPrueba.xlsx
+++ b/DeudoresPrueba.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>Consecutivo</t>
   </si>
@@ -37,6 +37,9 @@
     <t>ALISO</t>
   </si>
   <si>
+    <t>ARROZ PAISA SUBA</t>
+  </si>
+  <si>
     <t>CAMPO VERDE TOCANCIPA</t>
   </si>
   <si>
@@ -49,6 +52,9 @@
     <t>CARNILANDIA</t>
   </si>
   <si>
+    <t>CARNIVOROS</t>
+  </si>
+  <si>
     <t>CIMARRON DORADO</t>
   </si>
   <si>
@@ -85,7 +91,13 @@
     <t>LA SELECTA</t>
   </si>
   <si>
+    <t>LOS PAISANOS</t>
+  </si>
+  <si>
     <t>MAFE</t>
+  </si>
+  <si>
+    <t>MERKA FRUVER ALEJANDRO</t>
   </si>
   <si>
     <t>MERKA FRUVER DEXI</t>
@@ -474,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -536,10 +548,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="2">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="D4">
-        <v>540000</v>
+        <v>166000</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -553,10 +565,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="2">
-        <v>46051</v>
+        <v>46058</v>
       </c>
       <c r="D5">
-        <v>874300</v>
+        <v>635000</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -570,10 +582,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="D6">
-        <v>324500</v>
+        <v>385000</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -590,7 +602,7 @@
         <v>46056</v>
       </c>
       <c r="D7">
-        <v>620000</v>
+        <v>324500</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -607,7 +619,7 @@
         <v>46056</v>
       </c>
       <c r="D8">
-        <v>307000</v>
+        <v>620000</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -621,10 +633,10 @@
         <v>12</v>
       </c>
       <c r="C9" s="2">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="D9">
-        <v>122500</v>
+        <v>425000</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -638,10 +650,10 @@
         <v>13</v>
       </c>
       <c r="C10" s="2">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c r="D10">
-        <v>255000</v>
+        <v>459600</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -655,10 +667,10 @@
         <v>14</v>
       </c>
       <c r="C11" s="2">
-        <v>45921</v>
+        <v>46056</v>
       </c>
       <c r="D11">
-        <v>200000</v>
+        <v>122500</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -672,10 +684,10 @@
         <v>15</v>
       </c>
       <c r="C12" s="2">
-        <v>45947</v>
+        <v>46057</v>
       </c>
       <c r="D12">
-        <v>100000</v>
+        <v>85000</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -689,10 +701,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="2">
-        <v>46039</v>
+        <v>45921</v>
       </c>
       <c r="D13">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -706,10 +718,10 @@
         <v>17</v>
       </c>
       <c r="C14" s="2">
-        <v>46056</v>
+        <v>45947</v>
       </c>
       <c r="D14">
-        <v>298000</v>
+        <v>100000</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -723,10 +735,10 @@
         <v>18</v>
       </c>
       <c r="C15" s="2">
-        <v>46048</v>
+        <v>46039</v>
       </c>
       <c r="D15">
-        <v>107000</v>
+        <v>100000</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -743,7 +755,7 @@
         <v>46056</v>
       </c>
       <c r="D16">
-        <v>257700</v>
+        <v>298000</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -757,10 +769,10 @@
         <v>20</v>
       </c>
       <c r="C17" s="2">
-        <v>46056</v>
+        <v>46048</v>
       </c>
       <c r="D17">
-        <v>4101500</v>
+        <v>107000</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -774,10 +786,10 @@
         <v>21</v>
       </c>
       <c r="C18" s="2">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="D18">
-        <v>230700</v>
+        <v>257700</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -791,10 +803,10 @@
         <v>22</v>
       </c>
       <c r="C19" s="2">
-        <v>45912</v>
+        <v>46056</v>
       </c>
       <c r="D19">
-        <v>82000</v>
+        <v>4101500</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -808,10 +820,10 @@
         <v>23</v>
       </c>
       <c r="C20" s="2">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="D20">
-        <v>50000</v>
+        <v>230700</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -825,10 +837,10 @@
         <v>24</v>
       </c>
       <c r="C21" s="2">
-        <v>45988</v>
+        <v>45912</v>
       </c>
       <c r="D21">
-        <v>15400</v>
+        <v>82000</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -839,13 +851,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="2">
-        <v>45995</v>
+        <v>46058</v>
       </c>
       <c r="D22">
-        <v>339000</v>
+        <v>319000</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -856,13 +868,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23" s="2">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="D23">
-        <v>443900</v>
+        <v>50000</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -873,13 +885,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="2">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="D24">
-        <v>193800</v>
+        <v>338000</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -890,13 +902,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" s="2">
-        <v>46055</v>
+        <v>45995</v>
       </c>
       <c r="D25">
-        <v>116000</v>
+        <v>339000</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -910,10 +922,10 @@
         <v>28</v>
       </c>
       <c r="C26" s="2">
-        <v>45931</v>
+        <v>45988</v>
       </c>
       <c r="D26">
-        <v>82000</v>
+        <v>15400</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -927,10 +939,10 @@
         <v>29</v>
       </c>
       <c r="C27" s="2">
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="D27">
-        <v>100000</v>
+        <v>443900</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -944,10 +956,10 @@
         <v>30</v>
       </c>
       <c r="C28" s="2">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="D28">
-        <v>1881400</v>
+        <v>193800</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -964,7 +976,7 @@
         <v>46055</v>
       </c>
       <c r="D29">
-        <v>700400</v>
+        <v>116000</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -978,12 +990,97 @@
         <v>32</v>
       </c>
       <c r="C30" s="2">
+        <v>45931</v>
+      </c>
+      <c r="D30">
+        <v>82000</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="2">
+        <v>46053</v>
+      </c>
+      <c r="D31">
+        <v>100000</v>
+      </c>
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="2">
+        <v>46052</v>
+      </c>
+      <c r="D32">
+        <v>1151400</v>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="2">
         <v>46056</v>
       </c>
-      <c r="D30">
+      <c r="D33">
+        <v>504000</v>
+      </c>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="2">
+        <v>46055</v>
+      </c>
+      <c r="D34">
+        <v>400000</v>
+      </c>
+      <c r="E34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="2">
+        <v>46056</v>
+      </c>
+      <c r="D35">
         <v>176000</v>
       </c>
-      <c r="E30" t="b">
+      <c r="E35" t="b">
         <v>0</v>
       </c>
     </row>

--- a/DeudoresPrueba.xlsx
+++ b/DeudoresPrueba.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>Consecutivo</t>
   </si>
@@ -73,10 +73,7 @@
     <t>DOÑA SANDRA</t>
   </si>
   <si>
-    <t>EL CEBU</t>
-  </si>
-  <si>
-    <t>EL RUBY</t>
+    <t>EL RES</t>
   </si>
   <si>
     <t>FERROCAM</t>
@@ -486,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -514,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2">
-        <v>46052</v>
+        <v>46060</v>
       </c>
       <c r="D2">
-        <v>174000</v>
+        <v>153000</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -531,10 +528,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="2">
-        <v>46055</v>
+        <v>46060</v>
       </c>
       <c r="D3">
-        <v>63000</v>
+        <v>148000</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -599,10 +596,10 @@
         <v>10</v>
       </c>
       <c r="C7" s="2">
-        <v>46056</v>
+        <v>46059</v>
       </c>
       <c r="D7">
-        <v>324500</v>
+        <v>82000</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -613,13 +610,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2">
         <v>46056</v>
       </c>
       <c r="D8">
-        <v>620000</v>
+        <v>324500</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -630,13 +627,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2">
-        <v>46057</v>
+        <v>46060</v>
       </c>
       <c r="D9">
-        <v>425000</v>
+        <v>203000</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -647,13 +644,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="D10">
-        <v>459600</v>
+        <v>425000</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -664,13 +661,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="2">
-        <v>46056</v>
+        <v>46059</v>
       </c>
       <c r="D11">
-        <v>122500</v>
+        <v>459600</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -681,13 +678,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="2">
-        <v>46057</v>
+        <v>46060</v>
       </c>
       <c r="D12">
-        <v>85000</v>
+        <v>101000</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -698,13 +695,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="2">
-        <v>45921</v>
+        <v>46060</v>
       </c>
       <c r="D13">
-        <v>200000</v>
+        <v>170000</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -715,13 +712,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2">
-        <v>45947</v>
+        <v>45921</v>
       </c>
       <c r="D14">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -732,10 +729,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2">
-        <v>46039</v>
+        <v>45947</v>
       </c>
       <c r="D15">
         <v>100000</v>
@@ -749,13 +746,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="2">
-        <v>46056</v>
+        <v>46061</v>
       </c>
       <c r="D16">
-        <v>298000</v>
+        <v>160000</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -766,13 +763,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="2">
-        <v>46048</v>
+        <v>46060</v>
       </c>
       <c r="D17">
-        <v>107000</v>
+        <v>523300</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -783,7 +780,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="2">
         <v>46056</v>
@@ -800,13 +797,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="2">
         <v>46056</v>
       </c>
       <c r="D19">
-        <v>4101500</v>
+        <v>354500</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -817,13 +814,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2">
-        <v>46052</v>
+        <v>46061</v>
       </c>
       <c r="D20">
-        <v>230700</v>
+        <v>2901450</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -834,13 +831,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="2">
-        <v>45912</v>
+        <v>46059</v>
       </c>
       <c r="D21">
-        <v>82000</v>
+        <v>240000</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -851,13 +848,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22" s="2">
-        <v>46058</v>
+        <v>45912</v>
       </c>
       <c r="D22">
-        <v>319000</v>
+        <v>82000</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -868,13 +865,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" s="2">
-        <v>46051</v>
+        <v>46058</v>
       </c>
       <c r="D23">
-        <v>50000</v>
+        <v>319000</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
@@ -885,13 +882,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C24" s="2">
-        <v>46058</v>
+        <v>46051</v>
       </c>
       <c r="D24">
-        <v>338000</v>
+        <v>50000</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -902,13 +899,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="2">
-        <v>45995</v>
+        <v>46058</v>
       </c>
       <c r="D25">
-        <v>339000</v>
+        <v>338000</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -919,13 +916,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2">
-        <v>45988</v>
+        <v>45995</v>
       </c>
       <c r="D26">
-        <v>15400</v>
+        <v>339000</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -936,13 +933,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C27" s="2">
-        <v>46052</v>
+        <v>45988</v>
       </c>
       <c r="D27">
-        <v>443900</v>
+        <v>15400</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -953,13 +950,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2">
-        <v>46055</v>
+        <v>46052</v>
       </c>
       <c r="D28">
-        <v>193800</v>
+        <v>443900</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -970,13 +967,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C29" s="2">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="D29">
-        <v>116000</v>
+        <v>165000</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -987,13 +984,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C30" s="2">
-        <v>45931</v>
+        <v>46059</v>
       </c>
       <c r="D30">
-        <v>82000</v>
+        <v>150000</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -1004,13 +1001,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C31" s="2">
-        <v>46053</v>
+        <v>45931</v>
       </c>
       <c r="D31">
-        <v>100000</v>
+        <v>82000</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -1021,13 +1018,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C32" s="2">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="D32">
-        <v>1151400</v>
+        <v>100000</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -1038,13 +1035,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="2">
-        <v>46056</v>
+        <v>46052</v>
       </c>
       <c r="D33">
-        <v>504000</v>
+        <v>1151400</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -1055,13 +1052,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C34" s="2">
-        <v>46055</v>
+        <v>46060</v>
       </c>
       <c r="D34">
-        <v>400000</v>
+        <v>1693700</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -1072,15 +1069,49 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="2">
+        <v>46047</v>
+      </c>
+      <c r="D35">
+        <v>200200</v>
+      </c>
+      <c r="E35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2">
+        <v>46055</v>
+      </c>
+      <c r="D36">
+        <v>400000</v>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="C35" s="2">
-        <v>46056</v>
-      </c>
-      <c r="D35">
-        <v>176000</v>
-      </c>
-      <c r="E35" t="b">
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="2">
+        <v>46060</v>
+      </c>
+      <c r="D37">
+        <v>341000</v>
+      </c>
+      <c r="E37" t="b">
         <v>0</v>
       </c>
     </row>
